--- a/moduli/2-cassettiera/cassettiera_costi.xlsx
+++ b/moduli/2-cassettiera/cassettiera_costi.xlsx
@@ -21,18 +21,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t xml:space="preserve">Modulo 2 – Cassettiera: distinta e costi</t>
   </si>
   <si>
-    <t xml:space="preserve">Cassettiera fissa per la campata sinistra (3 cassetti) + cassetto appeso sotto il piano. Celle gialle = stime.</t>
+    <t xml:space="preserve">Cassettiera fissa per la campata sinistra (3 cassetti) + cassetto appeso. Prezzi verificati il 18/10/2026; celle gialle = stime.</t>
   </si>
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Articolo</t>
+    <t xml:space="preserve">Articolo (prodotto trovato)</t>
   </si>
   <si>
     <t xml:space="preserve">Uso</t>
@@ -53,67 +53,85 @@
     <t xml:space="preserve">Fonte prezzo</t>
   </si>
   <si>
+    <t xml:space="preserve">Negozio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legno</t>
   </si>
   <si>
-    <t xml:space="preserve">Multistrato pioppo 18 mm, mezzo pannello 1250×1250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scatola, frontali (taglio a pag. 'Taglio pannelli')</t>
+    <t xml:space="preserve">Multistrato pioppo 18 mm 1200×600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scatola e frontali (2 pannelli, schema nel manuale)</t>
   </si>
   <si>
     <t xml:space="preserve">pz</t>
   </si>
   <si>
+    <t xml:space="preserve">verificato 18/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnomat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il pannello intero da 18 non c'è a Tecnomat; LM al m² 59 €/m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multistrato pioppo 15 mm 1200×600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scatole dei 4 cassetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibra grezza (faesite) 3 mm 2500×1250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fondi dei cassetti e schienale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 mm invece di 4: va bene per carichi fino a ~15 kg per cassetto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferramenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coppia guide cassetto estrazione totale H45 L 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 cassettiera + 1 appeso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portata non indicata; LM Cisne-45 a sfere 50 kg a 10,90 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maniglie</t>
+  </si>
+  <si>
     <t xml:space="preserve">stima – da verificare</t>
   </si>
   <si>
-    <t xml:space="preserve">Multistrato pioppo 15 mm, mezzo pannello 1250×1250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scatole dei 4 cassetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDF 4 mm, pannello 2500×1250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fondi cassetti e schienale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferramenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guide a sfera estrazione totale 500 mm (coppia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 cassettiera + 1 appeso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maniglie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viti 4×45 (conf.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scatola cassettiera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viti 3,5×30, 3,5×25, 3×16, 4×16, 4×30, 4×50 (assortimento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cassetti, frontali, guide, fissaggio al tavolo</t>
+    <t xml:space="preserve">Viti 4×45, 3,5×30, 3,5×25, 3×16, 4×16, 4×30, 4×50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scatola, cassetti, frontali, guide, fissaggio</t>
   </si>
   <si>
     <t xml:space="preserve">set</t>
   </si>
   <si>
-    <t xml:space="preserve">Colla vinilica D3 (quota)</t>
+    <t xml:space="preserve">Collante vinilico D3 Tover 500 ml</t>
   </si>
   <si>
     <t xml:space="preserve">giunti</t>
@@ -122,10 +140,10 @@
     <t xml:space="preserve">Finitura</t>
   </si>
   <si>
-    <t xml:space="preserve">Vernice trasparente o olio 500 ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frontali e scatola</t>
+    <t xml:space="preserve">Impregnante legno all'acqua Cipir 0,75 l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scatola e frontali</t>
   </si>
   <si>
     <t xml:space="preserve">Prezzi verificati</t>
@@ -146,10 +164,13 @@
     <t xml:space="preserve">di cui finitura</t>
   </si>
   <si>
-    <t xml:space="preserve">Alternativa economica: scatola della cassettiera in OSB 18 ricavata dall'avanzo del pannello del tavolo base (0 €).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molti negozi tagliano il multistrato a misura: porta il foglio 'Taglio pannelli'.</t>
+    <t xml:space="preserve">da Tecnomat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternativa economica: scatola in OSB 18 dall'avanzo del pannello del tavolo base (0 €).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnomat taglia i pannelli in negozio: porta il foglio 'Taglio pannelli'.</t>
   </si>
   <si>
     <t xml:space="preserve">Pezzi da tagliare</t>
@@ -248,7 +269,7 @@
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;;\-#,##0.00&quot; €&quot;;\-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +323,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF1F5FA8"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -376,7 +405,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -405,11 +434,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -458,7 +495,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF1F5FA8"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -677,16 +714,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -724,130 +764,173 @@
       <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>35</v>
+        <v>17.8</v>
       </c>
       <c r="G5" s="8" t="n">
         <f aca="false">D5*F5</f>
-        <v>35</v>
+        <v>35.6</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="F6" s="7" t="n">
-        <v>30</v>
+        <v>15.9</v>
       </c>
       <c r="G6" s="8" t="n">
         <f aca="false">D6*F6</f>
-        <v>30</v>
+        <v>31.8</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">D7*F7</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>12</v>
+        <v>10.9</v>
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">D8*F8</f>
-        <v>48</v>
+        <v>43.6</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>4</v>
       </c>
       <c r="G9" s="8" t="n">
@@ -855,182 +938,196 @@
         <v>16</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>4</v>
+        <v>35</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="G10" s="8" t="n">
         <f aca="false">D10*F10</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>8</v>
+        <v>4.95</v>
       </c>
       <c r="G11" s="8" t="n">
         <f aca="false">D11*F11</f>
-        <v>8</v>
+        <v>4.95</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="G12" s="8" t="n">
         <f aca="false">D12*F12</f>
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <f aca="false">D13*F13</f>
-        <v>12</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G12,H5:H12,"verificato 18/10/2026")</f>
+        <v>138.65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="9" t="s">
-        <v>35</v>
+      <c r="F15" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="G15" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,H5:H13,"fornito da te")+SUMIFS(G5:G13,H5:H13,"OBI, verificato 18/10/2026")</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(G5:G12,H5:H12,"stima – da verificare")</f>
+        <v>26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,H5:H13,"stima – da verificare")</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <f aca="false">SUM(G5:G13)</f>
-        <v>172</v>
+      <c r="F16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <f aca="false">SUM(G5:G12)</f>
+        <v>164.65</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G12,A5:A12,"Legno")</f>
+        <v>83.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="9" t="s">
-        <v>38</v>
+      <c r="F19" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="G19" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,A5:A13,"Legno")</f>
-        <v>80</v>
+        <f aca="false">SUMIFS(G5:G12,A5:A12,"Ferramenta")</f>
+        <v>74.55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="9" t="s">
-        <v>39</v>
+      <c r="F20" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="G20" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,A5:A13,"Ferramenta")</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <f aca="false">SUMIFS(G5:G13,A5:A13,"Finitura")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>41</v>
+        <f aca="false">SUMIFS(G5:G12,A5:A12,"Finitura")</f>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <f aca="false">SUMIFS(G5:G12,I5:I12,"Tecnomat")</f>
+        <v>164.65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J5" r:id="rId1" display="apri"/>
+    <hyperlink ref="J6" r:id="rId2" display="apri"/>
+    <hyperlink ref="J7" r:id="rId3" display="apri"/>
+    <hyperlink ref="J8" r:id="rId4" display="apri"/>
+    <hyperlink ref="J11" r:id="rId5" display="apri"/>
+    <hyperlink ref="J12" r:id="rId6" display="apri"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1057,21 +1154,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>5</v>
@@ -1079,10 +1176,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>582</v>
@@ -1096,10 +1193,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>582</v>
@@ -1113,10 +1210,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>582</v>
@@ -1130,10 +1227,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>582</v>
@@ -1147,10 +1244,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>496</v>
@@ -1164,10 +1261,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>496</v>
@@ -1181,10 +1278,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>496</v>
@@ -1198,10 +1295,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>496</v>
@@ -1215,10 +1312,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>500</v>
@@ -1232,10 +1329,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>405</v>
@@ -1249,10 +1346,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>500</v>
@@ -1266,10 +1363,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>405</v>
@@ -1283,10 +1380,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>500</v>
@@ -1300,10 +1397,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>405</v>
@@ -1317,10 +1414,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>500</v>
@@ -1334,10 +1431,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>445</v>
@@ -1351,10 +1448,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>496</v>
@@ -1368,10 +1465,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>500</v>
@@ -1385,10 +1482,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>500</v>
@@ -1402,10 +1499,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>500</v>
@@ -1419,10 +1516,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>500</v>

--- a/moduli/2-cassettiera/cassettiera_costi.xlsx
+++ b/moduli/2-cassettiera/cassettiera_costi.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
   <si>
     <t xml:space="preserve">Modulo 2 – Cassettiera: distinta e costi</t>
   </si>
   <si>
-    <t xml:space="preserve">Cassettiera fissa per la campata sinistra (3 cassetti) + cassetto appeso. Prezzi verificati il 18/10/2026; celle gialle = stime.</t>
+    <t xml:space="preserve">Cassettiera fissa per la campata sinistra (3 cassetti). Prezzi verificati il 18/10/2026; celle gialle = stime.</t>
   </si>
   <si>
     <t xml:space="preserve">Categoria</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Multistrato pioppo 15 mm 1200×600</t>
   </si>
   <si>
-    <t xml:space="preserve">scatole dei 4 cassetti</t>
+    <t xml:space="preserve">scatole dei 3 cassetti</t>
   </si>
   <si>
     <t xml:space="preserve">Fibra grezza (faesite) 3 mm 2500×1250</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Coppia guide cassetto estrazione totale H45 L 500</t>
   </si>
   <si>
-    <t xml:space="preserve">3 cassettiera + 1 appeso</t>
+    <t xml:space="preserve">3 cassetti</t>
   </si>
   <si>
     <t xml:space="preserve">cp</t>
@@ -212,9 +212,6 @@
     <t xml:space="preserve">Frontale cassetto 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontale cassetto appeso</t>
-  </si>
-  <si>
     <t xml:space="preserve">multistrato 15</t>
   </si>
   <si>
@@ -236,13 +233,7 @@
     <t xml:space="preserve">cassetto 3: testata</t>
   </si>
   <si>
-    <t xml:space="preserve">appeso: fianco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appeso: testata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDF 4</t>
+    <t xml:space="preserve">pannello di fibra 3</t>
   </si>
   <si>
     <t xml:space="preserve">Cassettiera schienale</t>
@@ -255,9 +246,6 @@
   </si>
   <si>
     <t xml:space="preserve">cassetto 3: fondo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appeso: fondo</t>
   </si>
 </sst>
 </file>
@@ -821,7 +809,7 @@
         <v>22</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>16</v>
@@ -831,7 +819,7 @@
       </c>
       <c r="G6" s="8" t="n">
         <f aca="false">D6*F6</f>
-        <v>31.8</v>
+        <v>15.9</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>17</v>
@@ -891,7 +879,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>29</v>
@@ -901,7 +889,7 @@
       </c>
       <c r="G8" s="8" t="n">
         <f aca="false">D8*F8</f>
-        <v>43.6</v>
+        <v>32.7</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>17</v>
@@ -925,7 +913,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>16</v>
@@ -935,7 +923,7 @@
       </c>
       <c r="G9" s="8" t="n">
         <f aca="false">D9*F9</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>32</v>
@@ -1052,7 +1040,7 @@
       </c>
       <c r="G14" s="8" t="n">
         <f aca="false">SUMIFS(G5:G12,H5:H12,"verificato 18/10/2026")</f>
-        <v>138.65</v>
+        <v>111.85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1061,7 +1049,7 @@
       </c>
       <c r="G15" s="8" t="n">
         <f aca="false">SUMIFS(G5:G12,H5:H12,"stima – da verificare")</f>
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1070,7 +1058,7 @@
       </c>
       <c r="G16" s="13" t="n">
         <f aca="false">SUM(G5:G12)</f>
-        <v>164.65</v>
+        <v>133.85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1079,7 +1067,7 @@
       </c>
       <c r="G18" s="8" t="n">
         <f aca="false">SUMIFS(G5:G12,A5:A12,"Legno")</f>
-        <v>83.4</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1088,7 +1076,7 @@
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">SUMIFS(G5:G12,A5:A12,"Ferramenta")</f>
-        <v>74.55</v>
+        <v>59.65</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1106,7 +1094,7 @@
       </c>
       <c r="G22" s="8" t="n">
         <f aca="false">SUMIFS(G5:G12,I5:I12,"Tecnomat")</f>
-        <v>164.65</v>
+        <v>133.85</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,7 +1131,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -1182,7 +1170,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>400</v>
@@ -1199,7 +1187,7 @@
         <v>57</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>400</v>
@@ -1216,7 +1204,7 @@
         <v>58</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>460</v>
@@ -1233,7 +1221,7 @@
         <v>59</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>460</v>
@@ -1295,30 +1283,30 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>500</v>
+        <v>405</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>85</v>
@@ -1329,13 +1317,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>405</v>
+        <v>500</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>85</v>
@@ -1346,13 +1334,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>500</v>
+        <v>405</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>85</v>
@@ -1363,13 +1351,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>405</v>
+        <v>500</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>85</v>
@@ -1380,13 +1368,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>500</v>
+        <v>405</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>85</v>
@@ -1397,137 +1385,69 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>405</v>
+        <v>496</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>500</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>70</v>
+        <v>435</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>70</v>
+        <v>435</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>435</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>435</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>435</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>475</v>
-      </c>
-      <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
     </row>
